--- a/回後買上漲圖表_20260603/回後買上漲_標準版(1+2)_20260603.xlsx
+++ b/回後買上漲圖表_20260603/回後買上漲_標準版(1+2)_20260603.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="掃描標的" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,15 +28,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微軟正黑體"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F8"/>
+        <bgColor rgb="00F2F5F8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +88,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,10 +491,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
@@ -481,132 +559,1814 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1618.TW</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>6144</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>1027</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1513.TW</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>45918</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>8544</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1616.TW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>億泰</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3586</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>683</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>9933.TW</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>20295</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>3939</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>8076.TWO</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>伍豐</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6570</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1273</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1514.TW</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>22363</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>4536</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2031.TW</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4229</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>922</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>1612.TW</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>宏泰</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>5759</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>1332</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>5381.TWO</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>光譜</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4110</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>1529.TW</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>樂事綠能</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>2870</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>743</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>6873.TW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>泓德能源</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1553</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>5530.TWO</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>龍巖</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>3493</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>885</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>8104.TW</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>錸寶</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>11330</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2962</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2371.TW</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>大同</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>67652</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>17908</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>1447.TW</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>力鵬</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>8853</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2507</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>8182.TWO</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>加高</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>8575</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>2447</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>1217.TW</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>愛之味</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2975</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>864</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>9934.TW</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>成霖</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>921</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1609.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>大亞</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>31405</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>10576</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>3374.TWO</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>33215</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>11561</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2851.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>中再保</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1238</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>2484.TW</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>希華</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>35433</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>12604</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>6907.TWO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>雅特力-KY</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3834</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1442</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2030.TW</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>彰源</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>3463</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>1355</v>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2032.TW</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>新鋼</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>2256</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>969</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>1444.TW</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>力麗</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>10873</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>5013</v>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>1504.TW</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>95854</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>42978</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2493.TW</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>揚博</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>5998</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>2744</v>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>5210.TWO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>寶碩</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>5536.TWO</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>聖暉*</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>2195</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>1036</v>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2014.TW</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>中鴻</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>18193</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>8684</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2457.TW</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>飛宏</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>8254</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>4150</v>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6129.TWO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>普誠</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2583</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1306</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>3483.TWO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>力致</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
         <v>110.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D35" s="9" t="n">
         <v>103</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F35" s="11" t="n">
         <v>4239</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G35" s="11" t="n">
         <v>2088</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://tw.stock.yahoo.com/quote/3483</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6126.TWO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6126</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>42.65</v>
-      </c>
-      <c r="D3" t="n">
-        <v>39.15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>15696</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5991</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://tw.stock.yahoo.com/quote/6126</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2317.TW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>309</v>
-      </c>
-      <c r="D4" t="n">
-        <v>302</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>149311</v>
-      </c>
-      <c r="G4" t="n">
-        <v>110375</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>https://tw.stock.yahoo.com/quote/2317</t>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>3615.TWO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>12475</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>6701</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>3265.TWO</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>190</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>3104</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>1719</v>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>踩20MA</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2392.TW</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>正崴</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>7198</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>3912</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>3017.TW</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>2855</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>2835</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>6892</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>3844</v>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2442.TW</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>新美齊</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>3483</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2071</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>2351.TW</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>順德</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>206</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>8936</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>5143</v>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>踩20MA</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>4534.TWO</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>慶騰</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>2466</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>1444</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>未踩支撐</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>6227.TWO</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>茂綸</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>1304</v>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>5&gt;10&gt;20 多頭排列</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>踩10MA</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>